--- a/9/food/tm2026-sm.xlsx
+++ b/9/food/tm2026-sm.xlsx
@@ -7115,8 +7115,8 @@
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C100:D100"/>
     <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C100:D100"/>
     <mergeCell ref="C195:D195"/>
     <mergeCell ref="C157:D157"/>
     <mergeCell ref="C138:D138"/>

--- a/9/food/tm2026-sm.xlsx
+++ b/9/food/tm2026-sm.xlsx
@@ -7115,8 +7115,8 @@
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C62:D62"/>
     <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C62:D62"/>
     <mergeCell ref="C195:D195"/>
     <mergeCell ref="C157:D157"/>
     <mergeCell ref="C138:D138"/>
